--- a/pokeMAP.xlsx
+++ b/pokeMAP.xlsx
@@ -663,11 +663,11 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T2" s="2" t="n">
-        <v>187</v>
+        <v>66</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>125</v>
@@ -756,11 +756,11 @@
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T3" s="3" t="n">
-        <v>187</v>
+        <v>66</v>
       </c>
       <c r="U3" s="3" t="n">
         <v>100</v>
@@ -926,11 +926,11 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T5" s="3" t="n">
-        <v>190</v>
+        <v>69</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>125</v>
@@ -1019,11 +1019,11 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T6" s="2" t="n">
-        <v>190</v>
+        <v>69</v>
       </c>
       <c r="U6" s="2" t="n">
         <v>100</v>
@@ -1189,11 +1189,11 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T8" s="2" t="n">
-        <v>180</v>
+        <v>63</v>
       </c>
       <c r="U8" s="2" t="n">
         <v>125</v>
@@ -1282,11 +1282,11 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T9" s="3" t="n">
-        <v>180</v>
+        <v>63</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>100</v>
@@ -1448,11 +1448,11 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T11" s="3" t="n">
-        <v>152</v>
+        <v>53</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>62</v>
@@ -1537,11 +1537,11 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T12" s="2" t="n">
-        <v>152</v>
+        <v>53</v>
       </c>
       <c r="U12" s="2" t="n">
         <v>50</v>
@@ -1703,11 +1703,11 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T14" s="2" t="n">
-        <v>153</v>
+        <v>54</v>
       </c>
       <c r="U14" s="2" t="n">
         <v>62</v>
@@ -1796,11 +1796,11 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T15" s="3" t="n">
-        <v>153</v>
+        <v>54</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>50</v>
@@ -1962,11 +1962,11 @@
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T17" s="3" t="n">
-        <v>167</v>
+        <v>59</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>62</v>
@@ -2051,11 +2051,11 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T18" s="2" t="n">
-        <v>167</v>
+        <v>59</v>
       </c>
       <c r="U18" s="2" t="n">
         <v>50</v>
@@ -2217,11 +2217,11 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T20" s="2" t="n">
-        <v>149</v>
+        <v>51</v>
       </c>
       <c r="U20" s="2" t="n">
         <v>25</v>
@@ -2379,11 +2379,11 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T22" s="2" t="n">
-        <v>158</v>
+        <v>56</v>
       </c>
       <c r="U22" s="2" t="n">
         <v>50</v>
@@ -2545,11 +2545,11 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T24" s="2" t="n">
-        <v>157</v>
+        <v>55</v>
       </c>
       <c r="U24" s="2" t="n">
         <v>50</v>
@@ -2711,11 +2711,11 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T26" s="2" t="n">
-        <v>164</v>
+        <v>59</v>
       </c>
       <c r="U26" s="2" t="n">
         <v>50</v>
@@ -2877,11 +2877,11 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T28" s="2" t="n">
-        <v>173</v>
+        <v>62</v>
       </c>
       <c r="U28" s="2" t="n">
         <v>50</v>
@@ -3047,11 +3047,11 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T30" s="2" t="n">
-        <v>180</v>
+        <v>64</v>
       </c>
       <c r="U30" s="2" t="n">
         <v>125</v>
@@ -3140,11 +3140,11 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T31" s="3" t="n">
-        <v>180</v>
+        <v>64</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>100</v>
@@ -3310,11 +3310,11 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T33" s="3" t="n">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>125</v>
@@ -3403,11 +3403,11 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T34" s="2" t="n">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="U34" s="2" t="n">
         <v>100</v>
@@ -3569,11 +3569,11 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T36" s="2" t="n">
-        <v>178</v>
+        <v>63</v>
       </c>
       <c r="U36" s="2" t="n">
         <v>50</v>
@@ -3735,11 +3735,11 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T38" s="2" t="n">
-        <v>171</v>
+        <v>60</v>
       </c>
       <c r="U38" s="2" t="n">
         <v>50</v>
@@ -3901,11 +3901,11 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T40" s="2" t="n">
-        <v>175</v>
+        <v>62</v>
       </c>
       <c r="U40" s="2" t="n">
         <v>50</v>
@@ -4067,11 +4067,11 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T42" s="2" t="n">
-        <v>185</v>
+        <v>66</v>
       </c>
       <c r="U42" s="2" t="n">
         <v>125</v>
@@ -4160,11 +4160,11 @@
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T43" s="3" t="n">
-        <v>185</v>
+        <v>66</v>
       </c>
       <c r="U43" s="3" t="n">
         <v>100</v>
@@ -4253,11 +4253,11 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T44" s="2" t="n">
-        <v>176</v>
+        <v>64</v>
       </c>
       <c r="U44" s="2" t="n">
         <v>125</v>
@@ -4346,11 +4346,11 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T45" s="3" t="n">
-        <v>176</v>
+        <v>64</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>100</v>
@@ -4512,11 +4512,11 @@
       </c>
       <c r="S47" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T47" s="3" t="n">
-        <v>156</v>
+        <v>54</v>
       </c>
       <c r="U47" s="3" t="n">
         <v>50</v>
@@ -4678,11 +4678,11 @@
       </c>
       <c r="S49" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T49" s="3" t="n">
-        <v>163</v>
+        <v>58</v>
       </c>
       <c r="U49" s="3" t="n">
         <v>50</v>
@@ -4848,11 +4848,11 @@
       </c>
       <c r="S51" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T51" s="3" t="n">
-        <v>142</v>
+        <v>49</v>
       </c>
       <c r="U51" s="3" t="n">
         <v>50</v>
@@ -5014,11 +5014,11 @@
       </c>
       <c r="S53" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T53" s="3" t="n">
-        <v>172</v>
+        <v>62</v>
       </c>
       <c r="U53" s="3" t="n">
         <v>50</v>
@@ -5180,11 +5180,11 @@
       </c>
       <c r="S55" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T55" s="3" t="n">
-        <v>174</v>
+        <v>63</v>
       </c>
       <c r="U55" s="3" t="n">
         <v>50</v>
@@ -5346,11 +5346,11 @@
       </c>
       <c r="S57" s="3" t="inlineStr">
         <is>
-          <t>pvp_gl</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T57" s="3" t="n">
-        <v>211</v>
+        <v>74</v>
       </c>
       <c r="U57" s="3" t="n">
         <v>150</v>
@@ -5435,11 +5435,11 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>pvp_gl</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T58" s="2" t="n">
-        <v>211</v>
+        <v>74</v>
       </c>
       <c r="U58" s="2" t="n">
         <v>100</v>
@@ -5528,11 +5528,11 @@
       </c>
       <c r="S59" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T59" s="3" t="n">
-        <v>196</v>
+        <v>71</v>
       </c>
       <c r="U59" s="3" t="n">
         <v>50</v>
@@ -5698,11 +5698,11 @@
       </c>
       <c r="S61" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T61" s="3" t="n">
-        <v>184</v>
+        <v>65</v>
       </c>
       <c r="U61" s="3" t="n">
         <v>125</v>
@@ -5791,11 +5791,11 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T62" s="2" t="n">
-        <v>184</v>
+        <v>65</v>
       </c>
       <c r="U62" s="2" t="n">
         <v>100</v>
@@ -5961,11 +5961,11 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T64" s="2" t="n">
-        <v>191</v>
+        <v>72</v>
       </c>
       <c r="U64" s="2" t="n">
         <v>125</v>
@@ -6054,11 +6054,11 @@
       </c>
       <c r="S65" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T65" s="3" t="n">
-        <v>191</v>
+        <v>72</v>
       </c>
       <c r="U65" s="3" t="n">
         <v>100</v>
@@ -6224,11 +6224,11 @@
       </c>
       <c r="S67" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T67" s="3" t="n">
-        <v>198</v>
+        <v>72</v>
       </c>
       <c r="U67" s="3" t="n">
         <v>125</v>
@@ -6317,11 +6317,11 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T68" s="2" t="n">
-        <v>198</v>
+        <v>72</v>
       </c>
       <c r="U68" s="2" t="n">
         <v>100</v>
@@ -6487,11 +6487,11 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T70" s="2" t="n">
-        <v>174</v>
+        <v>64</v>
       </c>
       <c r="U70" s="2" t="n">
         <v>125</v>
@@ -6580,11 +6580,11 @@
       </c>
       <c r="S71" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T71" s="3" t="n">
-        <v>174</v>
+        <v>64</v>
       </c>
       <c r="U71" s="3" t="n">
         <v>100</v>
@@ -6746,11 +6746,11 @@
       </c>
       <c r="S73" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T73" s="3" t="n">
-        <v>180</v>
+        <v>63</v>
       </c>
       <c r="U73" s="3" t="n">
         <v>50</v>
@@ -6912,11 +6912,11 @@
       </c>
       <c r="S75" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T75" s="3" t="n">
-        <v>195</v>
+        <v>69</v>
       </c>
       <c r="U75" s="3" t="n">
         <v>125</v>
@@ -7005,11 +7005,11 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T76" s="2" t="n">
-        <v>195</v>
+        <v>69</v>
       </c>
       <c r="U76" s="2" t="n">
         <v>100</v>
@@ -7171,11 +7171,11 @@
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T78" s="2" t="n">
-        <v>173</v>
+        <v>63</v>
       </c>
       <c r="U78" s="2" t="n">
         <v>50</v>
@@ -7337,11 +7337,11 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T80" s="2" t="n">
-        <v>185</v>
+        <v>65</v>
       </c>
       <c r="U80" s="2" t="n">
         <v>50</v>
@@ -7507,11 +7507,11 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T82" s="2" t="n">
-        <v>202</v>
+        <v>73</v>
       </c>
       <c r="U82" s="2" t="n">
         <v>125</v>
@@ -7600,11 +7600,11 @@
       </c>
       <c r="S83" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T83" s="3" t="n">
-        <v>202</v>
+        <v>73</v>
       </c>
       <c r="U83" s="3" t="n">
         <v>100</v>
@@ -7697,11 +7697,11 @@
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T84" s="2" t="n">
-        <v>189</v>
+        <v>70</v>
       </c>
       <c r="U84" s="2" t="n">
         <v>50</v>
@@ -7786,11 +7786,11 @@
       </c>
       <c r="S85" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T85" s="3" t="n">
-        <v>169</v>
+        <v>62</v>
       </c>
       <c r="U85" s="3" t="n">
         <v>50</v>
@@ -7948,11 +7948,11 @@
       </c>
       <c r="S87" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T87" s="3" t="n">
-        <v>167</v>
+        <v>58</v>
       </c>
       <c r="U87" s="3" t="n">
         <v>50</v>
@@ -8114,11 +8114,11 @@
       </c>
       <c r="S89" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T89" s="3" t="n">
-        <v>193</v>
+        <v>68</v>
       </c>
       <c r="U89" s="3" t="n">
         <v>50</v>
@@ -8284,11 +8284,11 @@
       </c>
       <c r="S91" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T91" s="3" t="n">
-        <v>184</v>
+        <v>64</v>
       </c>
       <c r="U91" s="3" t="n">
         <v>50</v>
@@ -8450,11 +8450,11 @@
       </c>
       <c r="S93" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T93" s="3" t="n">
-        <v>184</v>
+        <v>70</v>
       </c>
       <c r="U93" s="3" t="n">
         <v>125</v>
@@ -8539,11 +8539,11 @@
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T94" s="2" t="n">
-        <v>184</v>
+        <v>70</v>
       </c>
       <c r="U94" s="2" t="n">
         <v>100</v>
@@ -8705,11 +8705,11 @@
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T96" s="2" t="n">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="U96" s="2" t="n">
         <v>50</v>
@@ -8802,11 +8802,11 @@
       </c>
       <c r="S97" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T97" s="3" t="n">
-        <v>171</v>
+        <v>59</v>
       </c>
       <c r="U97" s="3" t="n">
         <v>50</v>
@@ -8968,11 +8968,11 @@
       </c>
       <c r="S99" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T99" s="3" t="n">
-        <v>184</v>
+        <v>68</v>
       </c>
       <c r="U99" s="3" t="n">
         <v>50</v>
@@ -9134,11 +9134,11 @@
       </c>
       <c r="S101" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T101" s="3" t="n">
-        <v>163</v>
+        <v>57</v>
       </c>
       <c r="U101" s="3" t="n">
         <v>50</v>
@@ -9304,11 +9304,11 @@
       </c>
       <c r="S103" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T103" s="3" t="n">
-        <v>194</v>
+        <v>71</v>
       </c>
       <c r="U103" s="3" t="n">
         <v>50</v>
@@ -9474,11 +9474,11 @@
       </c>
       <c r="S105" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T105" s="3" t="n">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="U105" s="3" t="n">
         <v>50</v>
@@ -9790,11 +9790,11 @@
       </c>
       <c r="S109" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T109" s="3" t="n">
-        <v>186</v>
+        <v>65</v>
       </c>
       <c r="U109" s="3" t="n">
         <v>100</v>
@@ -9887,11 +9887,11 @@
       </c>
       <c r="S110" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T110" s="2" t="n">
-        <v>171</v>
+        <v>60</v>
       </c>
       <c r="U110" s="2" t="n">
         <v>50</v>
@@ -10053,11 +10053,11 @@
       </c>
       <c r="S112" s="2" t="inlineStr">
         <is>
-          <t>pve</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T112" s="2" t="n">
-        <v>231</v>
+        <v>81</v>
       </c>
       <c r="U112" s="2" t="n">
         <v>125</v>
@@ -10146,11 +10146,11 @@
       </c>
       <c r="S113" s="3" t="inlineStr">
         <is>
-          <t>pve</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T113" s="3" t="n">
-        <v>231</v>
+        <v>81</v>
       </c>
       <c r="U113" s="3" t="n">
         <v>100</v>
@@ -10239,7 +10239,7 @@
         </is>
       </c>
       <c r="T114" s="2" t="n">
-        <v>223</v>
+        <v>96</v>
       </c>
       <c r="U114" s="2" t="n">
         <v>50</v>
@@ -10328,11 +10328,11 @@
       </c>
       <c r="S115" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T115" s="3" t="n">
-        <v>202</v>
+        <v>71</v>
       </c>
       <c r="U115" s="3" t="n">
         <v>100</v>
@@ -10502,11 +10502,11 @@
       </c>
       <c r="S117" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T117" s="3" t="n">
-        <v>184</v>
+        <v>65</v>
       </c>
       <c r="U117" s="3" t="n">
         <v>125</v>
@@ -10599,11 +10599,11 @@
       </c>
       <c r="S118" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T118" s="2" t="n">
-        <v>184</v>
+        <v>65</v>
       </c>
       <c r="U118" s="2" t="n">
         <v>100</v>
@@ -10692,11 +10692,11 @@
       </c>
       <c r="S119" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T119" s="3" t="n">
-        <v>167</v>
+        <v>59</v>
       </c>
       <c r="U119" s="3" t="n">
         <v>50</v>
@@ -10854,11 +10854,11 @@
       </c>
       <c r="S121" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T121" s="3" t="n">
-        <v>176</v>
+        <v>64</v>
       </c>
       <c r="U121" s="3" t="n">
         <v>50</v>
@@ -11024,11 +11024,11 @@
       </c>
       <c r="S123" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T123" s="3" t="n">
-        <v>189</v>
+        <v>68</v>
       </c>
       <c r="U123" s="3" t="n">
         <v>50</v>
@@ -11117,11 +11117,11 @@
       </c>
       <c r="S124" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T124" s="2" t="n">
-        <v>192</v>
+        <v>70</v>
       </c>
       <c r="U124" s="2" t="n">
         <v>50</v>
@@ -11287,11 +11287,11 @@
       </c>
       <c r="S126" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T126" s="2" t="n">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="U126" s="2" t="n">
         <v>100</v>
@@ -11384,11 +11384,11 @@
       </c>
       <c r="S127" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T127" s="3" t="n">
-        <v>197</v>
+        <v>72</v>
       </c>
       <c r="U127" s="3" t="n">
         <v>100</v>
@@ -11639,7 +11639,7 @@
         </is>
       </c>
       <c r="T130" s="2" t="n">
-        <v>212</v>
+        <v>75</v>
       </c>
       <c r="U130" s="2" t="n">
         <v>400</v>
@@ -11943,11 +11943,11 @@
       </c>
       <c r="S134" s="2" t="inlineStr">
         <is>
-          <t>pvp_gl</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T134" s="2" t="n">
-        <v>211</v>
+        <v>74</v>
       </c>
       <c r="U134" s="2" t="n">
         <v>25</v>
@@ -12255,7 +12255,7 @@
         </is>
       </c>
       <c r="T138" s="2" t="n">
-        <v>202</v>
+        <v>75</v>
       </c>
       <c r="U138" s="2" t="n">
         <v>125</v>
@@ -12348,11 +12348,11 @@
       </c>
       <c r="S139" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T139" s="3" t="n">
-        <v>188</v>
+        <v>67</v>
       </c>
       <c r="U139" s="3" t="n">
         <v>50</v>
@@ -12514,11 +12514,11 @@
       </c>
       <c r="S141" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T141" s="3" t="n">
-        <v>181</v>
+        <v>66</v>
       </c>
       <c r="U141" s="3" t="n">
         <v>50</v>
@@ -13065,7 +13065,7 @@
         </is>
       </c>
       <c r="T148" s="2" t="n">
-        <v>225</v>
+        <v>80</v>
       </c>
       <c r="U148" s="2" t="n">
         <v>125</v>
@@ -13158,7 +13158,7 @@
         </is>
       </c>
       <c r="T149" s="3" t="n">
-        <v>225</v>
+        <v>80</v>
       </c>
       <c r="U149" s="3" t="n">
         <v>100</v>
@@ -13474,11 +13474,11 @@
       </c>
       <c r="S153" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T153" s="3" t="n">
-        <v>178</v>
+        <v>62</v>
       </c>
       <c r="U153" s="3" t="n">
         <v>125</v>
@@ -13567,11 +13567,11 @@
       </c>
       <c r="S154" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T154" s="2" t="n">
-        <v>178</v>
+        <v>62</v>
       </c>
       <c r="U154" s="2" t="n">
         <v>100</v>
@@ -13737,11 +13737,11 @@
       </c>
       <c r="S156" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T156" s="2" t="n">
-        <v>190</v>
+        <v>69</v>
       </c>
       <c r="U156" s="2" t="n">
         <v>125</v>
@@ -13830,11 +13830,11 @@
       </c>
       <c r="S157" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T157" s="3" t="n">
-        <v>190</v>
+        <v>69</v>
       </c>
       <c r="U157" s="3" t="n">
         <v>100</v>
@@ -14000,11 +14000,11 @@
       </c>
       <c r="S159" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T159" s="3" t="n">
-        <v>192</v>
+        <v>68</v>
       </c>
       <c r="U159" s="3" t="n">
         <v>125</v>
@@ -14093,11 +14093,11 @@
       </c>
       <c r="S160" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T160" s="2" t="n">
-        <v>192</v>
+        <v>68</v>
       </c>
       <c r="U160" s="2" t="n">
         <v>100</v>
@@ -14255,11 +14255,11 @@
       </c>
       <c r="S162" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T162" s="2" t="n">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="U162" s="2" t="n">
         <v>25</v>
@@ -14413,11 +14413,11 @@
       </c>
       <c r="S164" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T164" s="2" t="n">
-        <v>168</v>
+        <v>58</v>
       </c>
       <c r="U164" s="2" t="n">
         <v>50</v>
@@ -14575,11 +14575,11 @@
       </c>
       <c r="S166" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T166" s="2" t="n">
-        <v>143</v>
+        <v>52</v>
       </c>
       <c r="U166" s="2" t="n">
         <v>25</v>
@@ -14737,11 +14737,11 @@
       </c>
       <c r="S168" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T168" s="2" t="n">
-        <v>152</v>
+        <v>53</v>
       </c>
       <c r="U168" s="2" t="n">
         <v>50</v>
@@ -14976,11 +14976,11 @@
       </c>
       <c r="S171" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T171" s="3" t="n">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="U171" s="3" t="n">
         <v>50</v>
@@ -15142,11 +15142,11 @@
       </c>
       <c r="S173" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T173" s="3" t="n">
-        <v>164</v>
+        <v>59</v>
       </c>
       <c r="U173" s="3" t="n">
         <v>75</v>
@@ -15235,11 +15235,11 @@
       </c>
       <c r="S174" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T174" s="2" t="n">
-        <v>178</v>
+        <v>63</v>
       </c>
       <c r="U174" s="2" t="n">
         <v>75</v>
@@ -15328,11 +15328,11 @@
       </c>
       <c r="S175" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T175" s="3" t="n">
-        <v>175</v>
+        <v>62</v>
       </c>
       <c r="U175" s="3" t="n">
         <v>75</v>
@@ -15421,11 +15421,11 @@
       </c>
       <c r="S176" s="2" t="inlineStr">
         <is>
-          <t>pvp_gl</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T176" s="2" t="n">
-        <v>212</v>
+        <v>74</v>
       </c>
       <c r="U176" s="2" t="n">
         <v>125</v>
@@ -15514,11 +15514,11 @@
       </c>
       <c r="S177" s="3" t="inlineStr">
         <is>
-          <t>pvp_gl</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T177" s="3" t="n">
-        <v>212</v>
+        <v>74</v>
       </c>
       <c r="U177" s="3" t="n">
         <v>100</v>
@@ -15607,11 +15607,11 @@
       </c>
       <c r="S178" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T178" s="2" t="n">
-        <v>164</v>
+        <v>59</v>
       </c>
       <c r="U178" s="2" t="n">
         <v>50</v>
@@ -15773,11 +15773,11 @@
       </c>
       <c r="S180" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T180" s="2" t="n">
-        <v>191</v>
+        <v>69</v>
       </c>
       <c r="U180" s="2" t="n">
         <v>125</v>
@@ -15866,11 +15866,11 @@
       </c>
       <c r="S181" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T181" s="3" t="n">
-        <v>191</v>
+        <v>69</v>
       </c>
       <c r="U181" s="3" t="n">
         <v>100</v>
@@ -16109,11 +16109,11 @@
       </c>
       <c r="S184" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T184" s="2" t="n">
-        <v>158</v>
+        <v>57</v>
       </c>
       <c r="U184" s="2" t="n">
         <v>25</v>
@@ -16429,11 +16429,11 @@
       </c>
       <c r="S188" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T188" s="2" t="n">
-        <v>156</v>
+        <v>56</v>
       </c>
       <c r="U188" s="2" t="n">
         <v>125</v>
@@ -16522,11 +16522,11 @@
       </c>
       <c r="S189" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T189" s="3" t="n">
-        <v>156</v>
+        <v>56</v>
       </c>
       <c r="U189" s="3" t="n">
         <v>100</v>
@@ -16688,11 +16688,11 @@
       </c>
       <c r="S191" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T191" s="3" t="n">
-        <v>173</v>
+        <v>63</v>
       </c>
       <c r="U191" s="3" t="n">
         <v>100</v>
@@ -16781,11 +16781,11 @@
       </c>
       <c r="S192" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T192" s="2" t="n">
-        <v>165</v>
+        <v>59</v>
       </c>
       <c r="U192" s="2" t="n">
         <v>50</v>
@@ -16947,11 +16947,11 @@
       </c>
       <c r="S194" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T194" s="2" t="n">
-        <v>192</v>
+        <v>70</v>
       </c>
       <c r="U194" s="2" t="n">
         <v>100</v>
@@ -17044,11 +17044,11 @@
       </c>
       <c r="S195" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T195" s="3" t="n">
-        <v>175</v>
+        <v>62</v>
       </c>
       <c r="U195" s="3" t="n">
         <v>50</v>
@@ -17360,11 +17360,11 @@
       </c>
       <c r="S199" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T199" s="3" t="n">
-        <v>186</v>
+        <v>71</v>
       </c>
       <c r="U199" s="3" t="n">
         <v>100</v>
@@ -17534,11 +17534,11 @@
       </c>
       <c r="S201" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T201" s="3" t="n">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="U201" s="3" t="n">
         <v>100</v>
@@ -17858,11 +17858,11 @@
       </c>
       <c r="S205" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T205" s="3" t="n">
-        <v>173</v>
+        <v>60</v>
       </c>
       <c r="U205" s="3" t="n">
         <v>50</v>
@@ -18020,11 +18020,11 @@
       </c>
       <c r="S207" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T207" s="3" t="n">
-        <v>195</v>
+        <v>69</v>
       </c>
       <c r="U207" s="3" t="n">
         <v>50</v>
@@ -18113,11 +18113,11 @@
       </c>
       <c r="S208" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T208" s="2" t="n">
-        <v>189</v>
+        <v>66</v>
       </c>
       <c r="U208" s="2" t="n">
         <v>100</v>
@@ -18287,11 +18287,11 @@
       </c>
       <c r="S210" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T210" s="2" t="n">
-        <v>178</v>
+        <v>66</v>
       </c>
       <c r="U210" s="2" t="n">
         <v>50</v>
@@ -18453,11 +18453,11 @@
       </c>
       <c r="S212" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T212" s="2" t="n">
-        <v>193</v>
+        <v>70</v>
       </c>
       <c r="U212" s="2" t="n">
         <v>50</v>
@@ -18781,11 +18781,11 @@
       </c>
       <c r="S216" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T216" s="2" t="n">
-        <v>199</v>
+        <v>74</v>
       </c>
       <c r="U216" s="2" t="n">
         <v>100</v>
@@ -18870,11 +18870,11 @@
       </c>
       <c r="S217" s="3" t="inlineStr">
         <is>
-          <t>pve</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T217" s="3" t="n">
-        <v>238</v>
+        <v>84</v>
       </c>
       <c r="U217" s="3" t="n">
         <v>150</v>
@@ -18959,11 +18959,11 @@
       </c>
       <c r="S218" s="2" t="inlineStr">
         <is>
-          <t>pve</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T218" s="2" t="n">
-        <v>238</v>
+        <v>84</v>
       </c>
       <c r="U218" s="2" t="n">
         <v>100</v>
@@ -19048,11 +19048,11 @@
       </c>
       <c r="S219" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T219" s="3" t="n">
-        <v>152</v>
+        <v>52</v>
       </c>
       <c r="U219" s="3" t="n">
         <v>50</v>
@@ -19218,7 +19218,7 @@
         </is>
       </c>
       <c r="T221" s="3" t="n">
-        <v>210</v>
+        <v>76</v>
       </c>
       <c r="U221" s="3" t="n">
         <v>125</v>
@@ -19315,7 +19315,7 @@
         </is>
       </c>
       <c r="T222" s="2" t="n">
-        <v>210</v>
+        <v>76</v>
       </c>
       <c r="U222" s="2" t="n">
         <v>100</v>
@@ -19412,11 +19412,11 @@
       </c>
       <c r="S223" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T223" s="3" t="n">
-        <v>193</v>
+        <v>71</v>
       </c>
       <c r="U223" s="3" t="n">
         <v>50</v>
@@ -19501,11 +19501,11 @@
       </c>
       <c r="S224" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T224" s="2" t="n">
-        <v>168</v>
+        <v>61</v>
       </c>
       <c r="U224" s="2" t="n">
         <v>50</v>
@@ -19894,11 +19894,11 @@
       </c>
       <c r="S229" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T229" s="3" t="n">
-        <v>178</v>
+        <v>66</v>
       </c>
       <c r="U229" s="3" t="n">
         <v>50</v>
@@ -20137,11 +20137,11 @@
       </c>
       <c r="S232" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T232" s="2" t="n">
-        <v>198</v>
+        <v>71</v>
       </c>
       <c r="U232" s="2" t="n">
         <v>50</v>
@@ -20303,7 +20303,7 @@
         </is>
       </c>
       <c r="T234" s="2" t="n">
-        <v>202</v>
+        <v>75</v>
       </c>
       <c r="U234" s="2" t="n">
         <v>100</v>
@@ -20538,11 +20538,11 @@
       </c>
       <c r="S237" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T237" s="3" t="n">
-        <v>175</v>
+        <v>64</v>
       </c>
       <c r="U237" s="3" t="n">
         <v>25</v>
@@ -20704,11 +20704,11 @@
       </c>
       <c r="S239" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T239" s="3" t="n">
-        <v>176</v>
+        <v>65</v>
       </c>
       <c r="U239" s="3" t="n">
         <v>25</v>
@@ -20797,11 +20797,11 @@
       </c>
       <c r="S240" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T240" s="2" t="n">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="U240" s="2" t="n">
         <v>125</v>
@@ -20894,11 +20894,11 @@
       </c>
       <c r="S241" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T241" s="3" t="n">
-        <v>197</v>
+        <v>72</v>
       </c>
       <c r="U241" s="3" t="n">
         <v>125</v>
@@ -21364,7 +21364,7 @@
         </is>
       </c>
       <c r="T247" s="3" t="n">
-        <v>231</v>
+        <v>80</v>
       </c>
       <c r="U247" s="3" t="n">
         <v>125</v>
@@ -21457,7 +21457,7 @@
         </is>
       </c>
       <c r="T248" s="2" t="n">
-        <v>231</v>
+        <v>80</v>
       </c>
       <c r="U248" s="2" t="n">
         <v>100</v>
@@ -21846,11 +21846,11 @@
       </c>
       <c r="S253" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T253" s="3" t="n">
-        <v>183</v>
+        <v>67</v>
       </c>
       <c r="U253" s="3" t="n">
         <v>125</v>
@@ -21935,11 +21935,11 @@
       </c>
       <c r="S254" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T254" s="2" t="n">
-        <v>183</v>
+        <v>67</v>
       </c>
       <c r="U254" s="2" t="n">
         <v>100</v>
@@ -22101,11 +22101,11 @@
       </c>
       <c r="S256" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T256" s="2" t="n">
-        <v>187</v>
+        <v>70</v>
       </c>
       <c r="U256" s="2" t="n">
         <v>125</v>
@@ -22190,11 +22190,11 @@
       </c>
       <c r="S257" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T257" s="3" t="n">
-        <v>187</v>
+        <v>70</v>
       </c>
       <c r="U257" s="3" t="n">
         <v>100</v>
@@ -22360,11 +22360,11 @@
       </c>
       <c r="S259" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T259" s="3" t="n">
-        <v>199</v>
+        <v>71</v>
       </c>
       <c r="U259" s="3" t="n">
         <v>125</v>
@@ -22453,11 +22453,11 @@
       </c>
       <c r="S260" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T260" s="2" t="n">
-        <v>199</v>
+        <v>71</v>
       </c>
       <c r="U260" s="2" t="n">
         <v>100</v>
@@ -22623,11 +22623,11 @@
       </c>
       <c r="S262" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T262" s="2" t="n">
-        <v>157</v>
+        <v>55</v>
       </c>
       <c r="U262" s="2" t="n">
         <v>50</v>
@@ -22785,11 +22785,11 @@
       </c>
       <c r="S264" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T264" s="2" t="n">
-        <v>189</v>
+        <v>66</v>
       </c>
       <c r="U264" s="2" t="n">
         <v>125</v>
@@ -22870,11 +22870,11 @@
       </c>
       <c r="S265" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T265" s="3" t="n">
-        <v>189</v>
+        <v>66</v>
       </c>
       <c r="U265" s="3" t="n">
         <v>100</v>
@@ -22959,11 +22959,11 @@
       </c>
       <c r="S266" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T266" s="2" t="n">
-        <v>151</v>
+        <v>54</v>
       </c>
       <c r="U266" s="2" t="n">
         <v>62</v>
@@ -23048,11 +23048,11 @@
       </c>
       <c r="S267" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T267" s="3" t="n">
-        <v>151</v>
+        <v>54</v>
       </c>
       <c r="U267" s="3" t="n">
         <v>50</v>
@@ -23210,11 +23210,11 @@
       </c>
       <c r="S269" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T269" s="3" t="n">
-        <v>138</v>
+        <v>51</v>
       </c>
       <c r="U269" s="3" t="n">
         <v>50</v>
@@ -23372,11 +23372,11 @@
       </c>
       <c r="S271" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T271" s="3" t="n">
-        <v>173</v>
+        <v>61</v>
       </c>
       <c r="U271" s="3" t="n">
         <v>125</v>
@@ -23461,11 +23461,11 @@
       </c>
       <c r="S272" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T272" s="2" t="n">
-        <v>173</v>
+        <v>61</v>
       </c>
       <c r="U272" s="2" t="n">
         <v>100</v>
@@ -23627,11 +23627,11 @@
       </c>
       <c r="S274" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T274" s="2" t="n">
-        <v>172</v>
+        <v>63</v>
       </c>
       <c r="U274" s="2" t="n">
         <v>125</v>
@@ -23720,11 +23720,11 @@
       </c>
       <c r="S275" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T275" s="3" t="n">
-        <v>172</v>
+        <v>63</v>
       </c>
       <c r="U275" s="3" t="n">
         <v>100</v>
@@ -23886,11 +23886,11 @@
       </c>
       <c r="S277" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T277" s="3" t="n">
-        <v>155</v>
+        <v>55</v>
       </c>
       <c r="U277" s="3" t="n">
         <v>50</v>
@@ -24048,11 +24048,11 @@
       </c>
       <c r="S279" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T279" s="3" t="n">
-        <v>164</v>
+        <v>58</v>
       </c>
       <c r="U279" s="3" t="n">
         <v>50</v>
@@ -24214,11 +24214,11 @@
       </c>
       <c r="S281" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T281" s="3" t="n">
-        <v>196</v>
+        <v>71</v>
       </c>
       <c r="U281" s="3" t="n">
         <v>125</v>
@@ -24307,11 +24307,11 @@
       </c>
       <c r="S282" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T282" s="2" t="n">
-        <v>196</v>
+        <v>71</v>
       </c>
       <c r="U282" s="2" t="n">
         <v>100</v>
@@ -24473,11 +24473,11 @@
       </c>
       <c r="S284" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T284" s="2" t="n">
-        <v>168</v>
+        <v>61</v>
       </c>
       <c r="U284" s="2" t="n">
         <v>50</v>
@@ -24635,11 +24635,11 @@
       </c>
       <c r="S286" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T286" s="2" t="n">
-        <v>176</v>
+        <v>66</v>
       </c>
       <c r="U286" s="2" t="n">
         <v>50</v>
@@ -24797,7 +24797,7 @@
         </is>
       </c>
       <c r="T288" s="2" t="n">
-        <v>254</v>
+        <v>89</v>
       </c>
       <c r="U288" s="2" t="n">
         <v>125</v>
@@ -24882,7 +24882,7 @@
         </is>
       </c>
       <c r="T289" s="3" t="n">
-        <v>254</v>
+        <v>89</v>
       </c>
       <c r="U289" s="3" t="n">
         <v>100</v>
@@ -25036,11 +25036,11 @@
       </c>
       <c r="S291" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T291" s="3" t="n">
-        <v>157</v>
+        <v>57</v>
       </c>
       <c r="U291" s="3" t="n">
         <v>50</v>
@@ -25271,11 +25271,11 @@
       </c>
       <c r="S294" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T294" s="2" t="n">
-        <v>175</v>
+        <v>63</v>
       </c>
       <c r="U294" s="2" t="n">
         <v>62</v>
@@ -25360,11 +25360,11 @@
       </c>
       <c r="S295" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T295" s="3" t="n">
-        <v>175</v>
+        <v>63</v>
       </c>
       <c r="U295" s="3" t="n">
         <v>50</v>
@@ -25526,11 +25526,11 @@
       </c>
       <c r="S297" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T297" s="3" t="n">
-        <v>201</v>
+        <v>73</v>
       </c>
       <c r="U297" s="3" t="n">
         <v>50</v>
@@ -25696,11 +25696,11 @@
       </c>
       <c r="S299" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T299" s="3" t="n">
-        <v>158</v>
+        <v>57</v>
       </c>
       <c r="U299" s="3" t="n">
         <v>50</v>
@@ -25789,11 +25789,11 @@
       </c>
       <c r="S300" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T300" s="2" t="n">
-        <v>173</v>
+        <v>62</v>
       </c>
       <c r="U300" s="2" t="n">
         <v>50</v>
@@ -25874,11 +25874,11 @@
       </c>
       <c r="S301" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T301" s="3" t="n">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="U301" s="3" t="n">
         <v>50</v>
@@ -26194,7 +26194,7 @@
         </is>
       </c>
       <c r="T305" s="3" t="n">
-        <v>203</v>
+        <v>71</v>
       </c>
       <c r="U305" s="3" t="n">
         <v>125</v>
@@ -26287,7 +26287,7 @@
         </is>
       </c>
       <c r="T306" s="2" t="n">
-        <v>203</v>
+        <v>71</v>
       </c>
       <c r="U306" s="2" t="n">
         <v>100</v>
@@ -26449,11 +26449,11 @@
       </c>
       <c r="S308" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T308" s="2" t="n">
-        <v>143</v>
+        <v>50</v>
       </c>
       <c r="U308" s="2" t="n">
         <v>50</v>
@@ -26619,11 +26619,11 @@
       </c>
       <c r="S310" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T310" s="2" t="n">
-        <v>169</v>
+        <v>62</v>
       </c>
       <c r="U310" s="2" t="n">
         <v>50</v>
@@ -27093,11 +27093,11 @@
       </c>
       <c r="S316" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T316" s="2" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="U316" s="2" t="n">
         <v>100</v>
@@ -27186,11 +27186,11 @@
       </c>
       <c r="S317" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T317" s="3" t="n">
-        <v>168</v>
+        <v>58</v>
       </c>
       <c r="U317" s="3" t="n">
         <v>50</v>
@@ -27352,11 +27352,11 @@
       </c>
       <c r="S319" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T319" s="3" t="n">
-        <v>169</v>
+        <v>64</v>
       </c>
       <c r="U319" s="3" t="n">
         <v>50</v>
@@ -27518,11 +27518,11 @@
       </c>
       <c r="S321" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T321" s="3" t="n">
-        <v>187</v>
+        <v>65</v>
       </c>
       <c r="U321" s="3" t="n">
         <v>400</v>
@@ -27684,11 +27684,11 @@
       </c>
       <c r="S323" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T323" s="3" t="n">
-        <v>164</v>
+        <v>59</v>
       </c>
       <c r="U323" s="3" t="n">
         <v>50</v>
@@ -27931,11 +27931,11 @@
       </c>
       <c r="S326" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T326" s="2" t="n">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="U326" s="2" t="n">
         <v>50</v>
@@ -28166,11 +28166,11 @@
       </c>
       <c r="S329" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T329" s="3" t="n">
-        <v>182</v>
+        <v>66</v>
       </c>
       <c r="U329" s="3" t="n">
         <v>125</v>
@@ -28259,11 +28259,11 @@
       </c>
       <c r="S330" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T330" s="2" t="n">
-        <v>182</v>
+        <v>66</v>
       </c>
       <c r="U330" s="2" t="n">
         <v>100</v>
@@ -28429,11 +28429,11 @@
       </c>
       <c r="S332" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T332" s="2" t="n">
-        <v>168</v>
+        <v>62</v>
       </c>
       <c r="U332" s="2" t="n">
         <v>50</v>
@@ -28595,11 +28595,11 @@
       </c>
       <c r="S334" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T334" s="2" t="n">
-        <v>166</v>
+        <v>57</v>
       </c>
       <c r="U334" s="2" t="n">
         <v>400</v>
@@ -29081,11 +29081,11 @@
       </c>
       <c r="S340" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T340" s="2" t="n">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="U340" s="2" t="n">
         <v>50</v>
@@ -29243,11 +29243,11 @@
       </c>
       <c r="S342" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T342" s="2" t="n">
-        <v>173</v>
+        <v>64</v>
       </c>
       <c r="U342" s="2" t="n">
         <v>50</v>
@@ -29405,11 +29405,11 @@
       </c>
       <c r="S344" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T344" s="2" t="n">
-        <v>166</v>
+        <v>58</v>
       </c>
       <c r="U344" s="2" t="n">
         <v>50</v>
@@ -29571,11 +29571,11 @@
       </c>
       <c r="S346" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T346" s="2" t="n">
-        <v>173</v>
+        <v>60</v>
       </c>
       <c r="U346" s="2" t="n">
         <v>50</v>
@@ -29741,11 +29741,11 @@
       </c>
       <c r="S348" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T348" s="2" t="n">
-        <v>188</v>
+        <v>68</v>
       </c>
       <c r="U348" s="2" t="n">
         <v>50</v>
@@ -29911,7 +29911,7 @@
         </is>
       </c>
       <c r="T350" s="2" t="n">
-        <v>205</v>
+        <v>72</v>
       </c>
       <c r="U350" s="2" t="n">
         <v>100</v>
@@ -30211,11 +30211,11 @@
       </c>
       <c r="S354" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T354" s="2" t="n">
-        <v>168</v>
+        <v>62</v>
       </c>
       <c r="U354" s="2" t="n">
         <v>50</v>
@@ -30381,11 +30381,11 @@
       </c>
       <c r="S356" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T356" s="2" t="n">
-        <v>176</v>
+        <v>62</v>
       </c>
       <c r="U356" s="2" t="n">
         <v>125</v>
@@ -30478,11 +30478,11 @@
       </c>
       <c r="S357" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T357" s="3" t="n">
-        <v>176</v>
+        <v>62</v>
       </c>
       <c r="U357" s="3" t="n">
         <v>100</v>
@@ -30806,11 +30806,11 @@
       </c>
       <c r="S361" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T361" s="3" t="n">
-        <v>163</v>
+        <v>68</v>
       </c>
       <c r="U361" s="3" t="n">
         <v>25</v>
@@ -30895,11 +30895,11 @@
       </c>
       <c r="S362" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T362" s="2" t="n">
-        <v>166</v>
+        <v>58</v>
       </c>
       <c r="U362" s="2" t="n">
         <v>100</v>
@@ -31065,11 +31065,11 @@
       </c>
       <c r="S364" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T364" s="2" t="n">
-        <v>194</v>
+        <v>68</v>
       </c>
       <c r="U364" s="2" t="n">
         <v>125</v>
@@ -31158,11 +31158,11 @@
       </c>
       <c r="S365" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T365" s="3" t="n">
-        <v>194</v>
+        <v>68</v>
       </c>
       <c r="U365" s="3" t="n">
         <v>100</v>
@@ -31324,11 +31324,11 @@
       </c>
       <c r="S367" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T367" s="3" t="n">
-        <v>174</v>
+        <v>63</v>
       </c>
       <c r="U367" s="3" t="n">
         <v>50</v>
@@ -31721,7 +31721,7 @@
         </is>
       </c>
       <c r="T372" s="2" t="n">
-        <v>223</v>
+        <v>81</v>
       </c>
       <c r="U372" s="2" t="n">
         <v>125</v>
@@ -31814,7 +31814,7 @@
         </is>
       </c>
       <c r="T373" s="3" t="n">
-        <v>223</v>
+        <v>81</v>
       </c>
       <c r="U373" s="3" t="n">
         <v>100</v>
@@ -31984,7 +31984,7 @@
         </is>
       </c>
       <c r="T375" s="3" t="n">
-        <v>226</v>
+        <v>79</v>
       </c>
       <c r="U375" s="3" t="n">
         <v>125</v>
@@ -32077,7 +32077,7 @@
         </is>
       </c>
       <c r="T376" s="2" t="n">
-        <v>226</v>
+        <v>79</v>
       </c>
       <c r="U376" s="2" t="n">
         <v>100</v>
@@ -32993,11 +32993,11 @@
       </c>
       <c r="S388" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T388" s="2" t="n">
-        <v>198</v>
+        <v>70</v>
       </c>
       <c r="U388" s="2" t="n">
         <v>125</v>
@@ -33086,11 +33086,11 @@
       </c>
       <c r="S389" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T389" s="3" t="n">
-        <v>198</v>
+        <v>70</v>
       </c>
       <c r="U389" s="3" t="n">
         <v>100</v>
@@ -33252,11 +33252,11 @@
       </c>
       <c r="S391" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T391" s="3" t="n">
-        <v>181</v>
+        <v>67</v>
       </c>
       <c r="U391" s="3" t="n">
         <v>125</v>
@@ -33341,11 +33341,11 @@
       </c>
       <c r="S392" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T392" s="2" t="n">
-        <v>181</v>
+        <v>67</v>
       </c>
       <c r="U392" s="2" t="n">
         <v>100</v>
@@ -33503,11 +33503,11 @@
       </c>
       <c r="S394" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T394" s="2" t="n">
-        <v>193</v>
+        <v>69</v>
       </c>
       <c r="U394" s="2" t="n">
         <v>125</v>
@@ -33592,11 +33592,11 @@
       </c>
       <c r="S395" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T395" s="3" t="n">
-        <v>193</v>
+        <v>69</v>
       </c>
       <c r="U395" s="3" t="n">
         <v>100</v>
@@ -33758,11 +33758,11 @@
       </c>
       <c r="S397" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T397" s="3" t="n">
-        <v>188</v>
+        <v>70</v>
       </c>
       <c r="U397" s="3" t="n">
         <v>125</v>
@@ -33851,11 +33851,11 @@
       </c>
       <c r="S398" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T398" s="2" t="n">
-        <v>188</v>
+        <v>70</v>
       </c>
       <c r="U398" s="2" t="n">
         <v>100</v>
@@ -34017,11 +34017,11 @@
       </c>
       <c r="S400" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T400" s="2" t="n">
-        <v>156</v>
+        <v>55</v>
       </c>
       <c r="U400" s="2" t="n">
         <v>50</v>
@@ -34183,11 +34183,11 @@
       </c>
       <c r="S402" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T402" s="2" t="n">
-        <v>150</v>
+        <v>52</v>
       </c>
       <c r="U402" s="2" t="n">
         <v>50</v>
@@ -34349,11 +34349,11 @@
       </c>
       <c r="S404" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T404" s="2" t="n">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="U404" s="2" t="n">
         <v>125</v>
@@ -34442,11 +34442,11 @@
       </c>
       <c r="S405" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T405" s="3" t="n">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="U405" s="3" t="n">
         <v>100</v>
@@ -34612,11 +34612,11 @@
       </c>
       <c r="S407" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T407" s="3" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="U407" s="3" t="n">
         <v>125</v>
@@ -34782,7 +34782,7 @@
         </is>
       </c>
       <c r="T409" s="3" t="n">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="U409" s="3" t="n">
         <v>50</v>
@@ -34940,11 +34940,11 @@
       </c>
       <c r="S411" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T411" s="3" t="n">
-        <v>162</v>
+        <v>63</v>
       </c>
       <c r="U411" s="3" t="n">
         <v>50</v>
@@ -35097,16 +35097,16 @@
       </c>
       <c r="R413" s="3" t="inlineStr">
         <is>
-          <t>Wormadam</t>
+          <t>Mothim</t>
         </is>
       </c>
       <c r="S413" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T413" s="3" t="n">
-        <v>156</v>
+        <v>55</v>
       </c>
       <c r="U413" s="3" t="n">
         <v>50</v>
@@ -35337,11 +35337,11 @@
       </c>
       <c r="S416" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T416" s="2" t="n">
-        <v>164</v>
+        <v>56</v>
       </c>
       <c r="U416" s="2" t="n">
         <v>50</v>
@@ -35580,11 +35580,11 @@
       </c>
       <c r="S419" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T419" s="3" t="n">
-        <v>175</v>
+        <v>65</v>
       </c>
       <c r="U419" s="3" t="n">
         <v>50</v>
@@ -35742,11 +35742,11 @@
       </c>
       <c r="S421" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T421" s="3" t="n">
-        <v>162</v>
+        <v>57</v>
       </c>
       <c r="U421" s="3" t="n">
         <v>50</v>
@@ -35912,11 +35912,11 @@
       </c>
       <c r="S423" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T423" s="3" t="n">
-        <v>177</v>
+        <v>63</v>
       </c>
       <c r="U423" s="3" t="n">
         <v>50</v>
@@ -36155,11 +36155,11 @@
       </c>
       <c r="S426" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T426" s="2" t="n">
-        <v>188</v>
+        <v>68</v>
       </c>
       <c r="U426" s="2" t="n">
         <v>50</v>
@@ -36313,11 +36313,11 @@
       </c>
       <c r="S428" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T428" s="2" t="n">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="U428" s="2" t="n">
         <v>50</v>
@@ -36625,11 +36625,11 @@
       </c>
       <c r="S432" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T432" s="2" t="n">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="U432" s="2" t="n">
         <v>50</v>
@@ -36787,11 +36787,11 @@
       </c>
       <c r="S434" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T434" s="2" t="n">
-        <v>169</v>
+        <v>60</v>
       </c>
       <c r="U434" s="2" t="n">
         <v>50</v>
@@ -36880,11 +36880,11 @@
       </c>
       <c r="S435" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T435" s="3" t="n">
-        <v>176</v>
+        <v>63</v>
       </c>
       <c r="U435" s="3" t="n">
         <v>50</v>
@@ -37046,11 +37046,11 @@
       </c>
       <c r="S437" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T437" s="3" t="n">
-        <v>172</v>
+        <v>60</v>
       </c>
       <c r="U437" s="3" t="n">
         <v>50</v>
@@ -37212,11 +37212,11 @@
       </c>
       <c r="S439" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T439" s="3" t="n">
-        <v>166</v>
+        <v>58</v>
       </c>
       <c r="U439" s="3" t="n">
         <v>50</v>
@@ -37309,11 +37309,11 @@
       </c>
       <c r="S440" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T440" s="2" t="n">
-        <v>189</v>
+        <v>68</v>
       </c>
       <c r="U440" s="2" t="n">
         <v>100</v>
@@ -37402,7 +37402,7 @@
         </is>
       </c>
       <c r="T441" s="3" t="n">
-        <v>223</v>
+        <v>96</v>
       </c>
       <c r="U441" s="3" t="n">
         <v>75</v>
@@ -37645,7 +37645,7 @@
         </is>
       </c>
       <c r="T444" s="2" t="n">
-        <v>237</v>
+        <v>82</v>
       </c>
       <c r="U444" s="2" t="n">
         <v>125</v>
@@ -37734,7 +37734,7 @@
         </is>
       </c>
       <c r="T445" s="3" t="n">
-        <v>237</v>
+        <v>82</v>
       </c>
       <c r="U445" s="3" t="n">
         <v>100</v>
@@ -37900,7 +37900,7 @@
         </is>
       </c>
       <c r="T447" s="3" t="n">
-        <v>223</v>
+        <v>84</v>
       </c>
       <c r="U447" s="3" t="n">
         <v>50</v>
@@ -37989,11 +37989,11 @@
       </c>
       <c r="S448" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T448" s="2" t="n">
-        <v>179</v>
+        <v>67</v>
       </c>
       <c r="U448" s="2" t="n">
         <v>50</v>
@@ -38159,11 +38159,11 @@
       </c>
       <c r="S450" s="2" t="inlineStr">
         <is>
-          <t>pvp_gl</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T450" s="2" t="n">
-        <v>207</v>
+        <v>72</v>
       </c>
       <c r="U450" s="2" t="n">
         <v>50</v>
@@ -38329,11 +38329,11 @@
       </c>
       <c r="S452" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T452" s="2" t="n">
-        <v>178</v>
+        <v>63</v>
       </c>
       <c r="U452" s="2" t="n">
         <v>50</v>
@@ -38495,11 +38495,11 @@
       </c>
       <c r="S454" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T454" s="2" t="n">
-        <v>176</v>
+        <v>65</v>
       </c>
       <c r="U454" s="2" t="n">
         <v>50</v>
@@ -38738,11 +38738,11 @@
       </c>
       <c r="S457" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T457" s="3" t="n">
-        <v>156</v>
+        <v>53</v>
       </c>
       <c r="U457" s="3" t="n">
         <v>50</v>
@@ -38904,11 +38904,11 @@
       </c>
       <c r="S459" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T459" s="3" t="n">
-        <v>169</v>
+        <v>58</v>
       </c>
       <c r="U459" s="3" t="n">
         <v>50</v>
@@ -38997,11 +38997,11 @@
       </c>
       <c r="S460" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T460" s="2" t="n">
-        <v>174</v>
+        <v>62</v>
       </c>
       <c r="U460" s="2" t="n">
         <v>50</v>
@@ -41482,11 +41482,11 @@
       </c>
       <c r="S493" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T493" s="3" t="n">
-        <v>173</v>
+        <v>60</v>
       </c>
       <c r="U493" s="3" t="n">
         <v>125</v>
@@ -41571,11 +41571,11 @@
       </c>
       <c r="S494" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T494" s="2" t="n">
-        <v>173</v>
+        <v>60</v>
       </c>
       <c r="U494" s="2" t="n">
         <v>100</v>
@@ -41733,11 +41733,11 @@
       </c>
       <c r="S496" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T496" s="2" t="n">
-        <v>197</v>
+        <v>73</v>
       </c>
       <c r="U496" s="2" t="n">
         <v>125</v>
@@ -41822,11 +41822,11 @@
       </c>
       <c r="S497" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T497" s="3" t="n">
-        <v>197</v>
+        <v>73</v>
       </c>
       <c r="U497" s="3" t="n">
         <v>100</v>
@@ -41984,11 +41984,11 @@
       </c>
       <c r="S499" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T499" s="3" t="n">
-        <v>191</v>
+        <v>69</v>
       </c>
       <c r="U499" s="3" t="n">
         <v>125</v>
@@ -42073,11 +42073,11 @@
       </c>
       <c r="S500" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T500" s="2" t="n">
-        <v>191</v>
+        <v>69</v>
       </c>
       <c r="U500" s="2" t="n">
         <v>100</v>
@@ -42235,11 +42235,11 @@
       </c>
       <c r="S502" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T502" s="2" t="n">
-        <v>153</v>
+        <v>53</v>
       </c>
       <c r="U502" s="2" t="n">
         <v>50</v>
@@ -42393,11 +42393,11 @@
       </c>
       <c r="S504" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T504" s="2" t="n">
-        <v>191</v>
+        <v>68</v>
       </c>
       <c r="U504" s="2" t="n">
         <v>125</v>
@@ -42478,11 +42478,11 @@
       </c>
       <c r="S505" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T505" s="3" t="n">
-        <v>191</v>
+        <v>68</v>
       </c>
       <c r="U505" s="3" t="n">
         <v>100</v>
@@ -42640,11 +42640,11 @@
       </c>
       <c r="S507" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T507" s="3" t="n">
-        <v>154</v>
+        <v>55</v>
       </c>
       <c r="U507" s="3" t="n">
         <v>50</v>
@@ -42806,11 +42806,11 @@
       </c>
       <c r="S509" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T509" s="3" t="n">
-        <v>170</v>
+        <v>62</v>
       </c>
       <c r="U509" s="3" t="n">
         <v>50</v>
@@ -42972,11 +42972,11 @@
       </c>
       <c r="S511" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T511" s="3" t="n">
-        <v>170</v>
+        <v>62</v>
       </c>
       <c r="U511" s="3" t="n">
         <v>50</v>
@@ -43138,11 +43138,11 @@
       </c>
       <c r="S513" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T513" s="3" t="n">
-        <v>170</v>
+        <v>62</v>
       </c>
       <c r="U513" s="3" t="n">
         <v>50</v>
@@ -43304,11 +43304,11 @@
       </c>
       <c r="S515" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T515" s="3" t="n">
-        <v>195</v>
+        <v>68</v>
       </c>
       <c r="U515" s="3" t="n">
         <v>50</v>
@@ -43470,11 +43470,11 @@
       </c>
       <c r="S517" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T517" s="3" t="n">
-        <v>183</v>
+        <v>68</v>
       </c>
       <c r="U517" s="3" t="n">
         <v>62</v>
@@ -43559,11 +43559,11 @@
       </c>
       <c r="S518" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T518" s="2" t="n">
-        <v>183</v>
+        <v>68</v>
       </c>
       <c r="U518" s="2" t="n">
         <v>50</v>
@@ -43721,11 +43721,11 @@
       </c>
       <c r="S520" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T520" s="2" t="n">
-        <v>172</v>
+        <v>63</v>
       </c>
       <c r="U520" s="2" t="n">
         <v>50</v>
@@ -43883,11 +43883,11 @@
       </c>
       <c r="S522" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T522" s="2" t="n">
-        <v>205</v>
+        <v>73</v>
       </c>
       <c r="U522" s="2" t="n">
         <v>250</v>
@@ -43972,11 +43972,11 @@
       </c>
       <c r="S523" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T523" s="3" t="n">
-        <v>205</v>
+        <v>73</v>
       </c>
       <c r="U523" s="3" t="n">
         <v>200</v>
@@ -44134,11 +44134,11 @@
       </c>
       <c r="S525" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T525" s="3" t="n">
-        <v>150</v>
+        <v>52</v>
       </c>
       <c r="U525" s="3" t="n">
         <v>50</v>
@@ -44300,7 +44300,7 @@
         </is>
       </c>
       <c r="T527" s="3" t="n">
-        <v>206</v>
+        <v>76</v>
       </c>
       <c r="U527" s="3" t="n">
         <v>50</v>
@@ -44535,7 +44535,7 @@
         </is>
       </c>
       <c r="T530" s="2" t="n">
-        <v>210</v>
+        <v>76</v>
       </c>
       <c r="U530" s="2" t="n">
         <v>250</v>
@@ -44624,7 +44624,7 @@
         </is>
       </c>
       <c r="T531" s="3" t="n">
-        <v>210</v>
+        <v>76</v>
       </c>
       <c r="U531" s="3" t="n">
         <v>200</v>
@@ -44782,11 +44782,11 @@
       </c>
       <c r="S533" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T533" s="3" t="n">
-        <v>183</v>
+        <v>66</v>
       </c>
       <c r="U533" s="3" t="n">
         <v>125</v>
@@ -44871,11 +44871,11 @@
       </c>
       <c r="S534" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T534" s="2" t="n">
-        <v>183</v>
+        <v>66</v>
       </c>
       <c r="U534" s="2" t="n">
         <v>100</v>
@@ -45195,11 +45195,11 @@
       </c>
       <c r="S538" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T538" s="2" t="n">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="U538" s="2" t="n">
         <v>125</v>
@@ -45284,11 +45284,11 @@
       </c>
       <c r="S539" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T539" s="3" t="n">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="U539" s="3" t="n">
         <v>100</v>
@@ -45446,11 +45446,11 @@
       </c>
       <c r="S541" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T541" s="3" t="n">
-        <v>173</v>
+        <v>62</v>
       </c>
       <c r="U541" s="3" t="n">
         <v>125</v>
@@ -45535,11 +45535,11 @@
       </c>
       <c r="S542" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T542" s="2" t="n">
-        <v>173</v>
+        <v>62</v>
       </c>
       <c r="U542" s="2" t="n">
         <v>100</v>
@@ -45697,11 +45697,11 @@
       </c>
       <c r="S544" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T544" s="2" t="n">
-        <v>162</v>
+        <v>56</v>
       </c>
       <c r="U544" s="2" t="n">
         <v>50</v>
@@ -45863,11 +45863,11 @@
       </c>
       <c r="S546" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T546" s="2" t="n">
-        <v>176</v>
+        <v>65</v>
       </c>
       <c r="U546" s="2" t="n">
         <v>50</v>
@@ -46102,11 +46102,11 @@
       </c>
       <c r="S549" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T549" s="3" t="n">
-        <v>199</v>
+        <v>72</v>
       </c>
       <c r="U549" s="3" t="n">
         <v>125</v>
@@ -46191,11 +46191,11 @@
       </c>
       <c r="S550" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T550" s="2" t="n">
-        <v>199</v>
+        <v>72</v>
       </c>
       <c r="U550" s="2" t="n">
         <v>100</v>
@@ -46357,7 +46357,7 @@
         </is>
       </c>
       <c r="T552" s="2" t="n">
-        <v>198</v>
+        <v>75</v>
       </c>
       <c r="U552" s="2" t="n">
         <v>50</v>
@@ -46596,11 +46596,11 @@
       </c>
       <c r="S555" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T555" s="3" t="n">
-        <v>180</v>
+        <v>64</v>
       </c>
       <c r="U555" s="3" t="n">
         <v>50</v>
@@ -46758,11 +46758,11 @@
       </c>
       <c r="S557" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T557" s="3" t="n">
-        <v>173</v>
+        <v>60</v>
       </c>
       <c r="U557" s="3" t="n">
         <v>50</v>
@@ -47001,11 +47001,11 @@
       </c>
       <c r="S560" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T560" s="2" t="n">
-        <v>173</v>
+        <v>60</v>
       </c>
       <c r="U560" s="2" t="n">
         <v>50</v>
@@ -47163,11 +47163,11 @@
       </c>
       <c r="S562" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T562" s="2" t="n">
-        <v>183</v>
+        <v>65</v>
       </c>
       <c r="U562" s="2" t="n">
         <v>50</v>
@@ -47329,7 +47329,7 @@
         </is>
       </c>
       <c r="T564" s="2" t="n">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="U564" s="2" t="n">
         <v>50</v>
@@ -47487,11 +47487,11 @@
       </c>
       <c r="S566" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T566" s="2" t="n">
-        <v>172</v>
+        <v>61</v>
       </c>
       <c r="U566" s="2" t="n">
         <v>50</v>
@@ -47649,11 +47649,11 @@
       </c>
       <c r="S568" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T568" s="2" t="n">
-        <v>176</v>
+        <v>66</v>
       </c>
       <c r="U568" s="2" t="n">
         <v>50</v>
@@ -47807,11 +47807,11 @@
       </c>
       <c r="S570" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T570" s="2" t="n">
-        <v>167</v>
+        <v>61</v>
       </c>
       <c r="U570" s="2" t="n">
         <v>50</v>
@@ -47969,11 +47969,11 @@
       </c>
       <c r="S572" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T572" s="2" t="n">
-        <v>176</v>
+        <v>62</v>
       </c>
       <c r="U572" s="2" t="n">
         <v>125</v>
@@ -48058,11 +48058,11 @@
       </c>
       <c r="S573" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T573" s="3" t="n">
-        <v>176</v>
+        <v>62</v>
       </c>
       <c r="U573" s="3" t="n">
         <v>100</v>
@@ -48220,11 +48220,11 @@
       </c>
       <c r="S575" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T575" s="3" t="n">
-        <v>197</v>
+        <v>71</v>
       </c>
       <c r="U575" s="3" t="n">
         <v>125</v>
@@ -48309,11 +48309,11 @@
       </c>
       <c r="S576" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T576" s="2" t="n">
-        <v>197</v>
+        <v>71</v>
       </c>
       <c r="U576" s="2" t="n">
         <v>100</v>
@@ -48475,11 +48475,11 @@
       </c>
       <c r="S578" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T578" s="2" t="n">
-        <v>163</v>
+        <v>58</v>
       </c>
       <c r="U578" s="2" t="n">
         <v>50</v>
@@ -48641,11 +48641,11 @@
       </c>
       <c r="S580" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T580" s="2" t="n">
-        <v>186</v>
+        <v>67</v>
       </c>
       <c r="U580" s="2" t="n">
         <v>125</v>
@@ -48730,11 +48730,11 @@
       </c>
       <c r="S581" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T581" s="3" t="n">
-        <v>186</v>
+        <v>67</v>
       </c>
       <c r="U581" s="3" t="n">
         <v>100</v>
@@ -48892,11 +48892,11 @@
       </c>
       <c r="S583" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T583" s="3" t="n">
-        <v>174</v>
+        <v>63</v>
       </c>
       <c r="U583" s="3" t="n">
         <v>50</v>
@@ -49127,11 +49127,11 @@
       </c>
       <c r="S586" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T586" s="2" t="n">
-        <v>189</v>
+        <v>68</v>
       </c>
       <c r="U586" s="2" t="n">
         <v>200</v>
@@ -49293,11 +49293,11 @@
       </c>
       <c r="S588" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T588" s="2" t="n">
-        <v>173</v>
+        <v>61</v>
       </c>
       <c r="U588" s="2" t="n">
         <v>50</v>
@@ -49459,11 +49459,11 @@
       </c>
       <c r="S590" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T590" s="2" t="n">
-        <v>180</v>
+        <v>63</v>
       </c>
       <c r="U590" s="2" t="n">
         <v>50</v>
@@ -49694,11 +49694,11 @@
       </c>
       <c r="S593" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T593" s="3" t="n">
-        <v>166</v>
+        <v>60</v>
       </c>
       <c r="U593" s="3" t="n">
         <v>50</v>
@@ -49856,11 +49856,11 @@
       </c>
       <c r="S595" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T595" s="3" t="n">
-        <v>177</v>
+        <v>61</v>
       </c>
       <c r="U595" s="3" t="n">
         <v>50</v>
@@ -50018,11 +50018,11 @@
       </c>
       <c r="S597" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T597" s="3" t="n">
-        <v>182</v>
+        <v>65</v>
       </c>
       <c r="U597" s="3" t="n">
         <v>125</v>
@@ -50107,11 +50107,11 @@
       </c>
       <c r="S598" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T598" s="2" t="n">
-        <v>182</v>
+        <v>65</v>
       </c>
       <c r="U598" s="2" t="n">
         <v>100</v>
@@ -50269,11 +50269,11 @@
       </c>
       <c r="S600" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T600" s="2" t="n">
-        <v>184</v>
+        <v>67</v>
       </c>
       <c r="U600" s="2" t="n">
         <v>125</v>
@@ -50362,11 +50362,11 @@
       </c>
       <c r="S601" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T601" s="3" t="n">
-        <v>184</v>
+        <v>67</v>
       </c>
       <c r="U601" s="3" t="n">
         <v>100</v>
@@ -50528,11 +50528,11 @@
       </c>
       <c r="S603" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T603" s="3" t="n">
-        <v>183</v>
+        <v>67</v>
       </c>
       <c r="U603" s="3" t="n">
         <v>50</v>
@@ -50690,11 +50690,11 @@
       </c>
       <c r="S605" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T605" s="3" t="n">
-        <v>199</v>
+        <v>74</v>
       </c>
       <c r="U605" s="3" t="n">
         <v>125</v>
@@ -50783,11 +50783,11 @@
       </c>
       <c r="S606" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T606" s="2" t="n">
-        <v>199</v>
+        <v>74</v>
       </c>
       <c r="U606" s="2" t="n">
         <v>100</v>
@@ -50953,7 +50953,7 @@
         </is>
       </c>
       <c r="T608" s="2" t="n">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="U608" s="2" t="n">
         <v>125</v>
@@ -51042,7 +51042,7 @@
         </is>
       </c>
       <c r="T609" s="3" t="n">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="U609" s="3" t="n">
         <v>100</v>
@@ -51200,11 +51200,11 @@
       </c>
       <c r="S611" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T611" s="3" t="n">
-        <v>197</v>
+        <v>72</v>
       </c>
       <c r="U611" s="3" t="n">
         <v>50</v>
@@ -51435,11 +51435,11 @@
       </c>
       <c r="S614" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T614" s="2" t="n">
-        <v>174</v>
+        <v>65</v>
       </c>
       <c r="U614" s="2" t="n">
         <v>200</v>
@@ -51670,11 +51670,11 @@
       </c>
       <c r="S617" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T617" s="3" t="n">
-        <v>180</v>
+        <v>69</v>
       </c>
       <c r="U617" s="3" t="n">
         <v>50</v>
@@ -51905,11 +51905,11 @@
       </c>
       <c r="S620" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T620" s="2" t="n">
-        <v>189</v>
+        <v>69</v>
       </c>
       <c r="U620" s="2" t="n">
         <v>50</v>
@@ -52071,7 +52071,7 @@
         </is>
       </c>
       <c r="T622" s="2" t="n">
-        <v>223</v>
+        <v>78</v>
       </c>
       <c r="U622" s="2" t="n">
         <v>150</v>
@@ -52160,7 +52160,7 @@
         </is>
       </c>
       <c r="T623" s="3" t="n">
-        <v>223</v>
+        <v>78</v>
       </c>
       <c r="U623" s="3" t="n">
         <v>100</v>
@@ -52322,11 +52322,11 @@
       </c>
       <c r="S625" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T625" s="3" t="n">
-        <v>200</v>
+        <v>73</v>
       </c>
       <c r="U625" s="3" t="n">
         <v>50</v>
@@ -52484,11 +52484,11 @@
       </c>
       <c r="S627" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T627" s="3" t="n">
-        <v>181</v>
+        <v>66</v>
       </c>
       <c r="U627" s="3" t="n">
         <v>50</v>
@@ -52812,7 +52812,7 @@
         </is>
       </c>
       <c r="T631" s="3" t="n">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="U631" s="3" t="n">
         <v>125</v>
@@ -52901,7 +52901,7 @@
         </is>
       </c>
       <c r="T632" s="2" t="n">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="U632" s="2" t="n">
         <v>100</v>
@@ -53063,7 +53063,7 @@
         </is>
       </c>
       <c r="T634" s="2" t="n">
-        <v>217</v>
+        <v>78</v>
       </c>
       <c r="U634" s="2" t="n">
         <v>400</v>
@@ -54097,11 +54097,11 @@
       </c>
       <c r="S648" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T648" s="2" t="n">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="U648" s="2" t="n">
         <v>125</v>
@@ -54186,11 +54186,11 @@
       </c>
       <c r="S649" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T649" s="3" t="n">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="U649" s="3" t="n">
         <v>100</v>
@@ -54348,11 +54348,11 @@
       </c>
       <c r="S651" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T651" s="3" t="n">
-        <v>196</v>
+        <v>71</v>
       </c>
       <c r="U651" s="3" t="n">
         <v>125</v>
@@ -54437,11 +54437,11 @@
       </c>
       <c r="S652" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T652" s="2" t="n">
-        <v>196</v>
+        <v>71</v>
       </c>
       <c r="U652" s="2" t="n">
         <v>100</v>
@@ -54599,11 +54599,11 @@
       </c>
       <c r="S654" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T654" s="2" t="n">
-        <v>178</v>
+        <v>66</v>
       </c>
       <c r="U654" s="2" t="n">
         <v>125</v>
@@ -54688,11 +54688,11 @@
       </c>
       <c r="S655" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T655" s="3" t="n">
-        <v>178</v>
+        <v>66</v>
       </c>
       <c r="U655" s="3" t="n">
         <v>100</v>
@@ -54846,11 +54846,11 @@
       </c>
       <c r="S657" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T657" s="3" t="n">
-        <v>151</v>
+        <v>54</v>
       </c>
       <c r="U657" s="3" t="n">
         <v>50</v>
@@ -55008,11 +55008,11 @@
       </c>
       <c r="S659" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T659" s="3" t="n">
-        <v>168</v>
+        <v>60</v>
       </c>
       <c r="U659" s="3" t="n">
         <v>125</v>
@@ -55097,11 +55097,11 @@
       </c>
       <c r="S660" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T660" s="2" t="n">
-        <v>168</v>
+        <v>60</v>
       </c>
       <c r="U660" s="2" t="n">
         <v>100</v>
@@ -55259,11 +55259,11 @@
       </c>
       <c r="S662" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T662" s="2" t="n">
-        <v>156</v>
+        <v>56</v>
       </c>
       <c r="U662" s="2" t="n">
         <v>125</v>
@@ -55348,11 +55348,11 @@
       </c>
       <c r="S663" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T663" s="3" t="n">
-        <v>156</v>
+        <v>56</v>
       </c>
       <c r="U663" s="3" t="n">
         <v>100</v>
@@ -55510,11 +55510,11 @@
       </c>
       <c r="S665" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T665" s="3" t="n">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="U665" s="3" t="n">
         <v>50</v>
@@ -55672,11 +55672,11 @@
       </c>
       <c r="S667" s="3" t="inlineStr">
         <is>
-          <t>pvp_gl</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T667" s="3" t="n">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="U667" s="3" t="n">
         <v>125</v>
@@ -55761,11 +55761,11 @@
       </c>
       <c r="S668" s="2" t="inlineStr">
         <is>
-          <t>pvp_gl</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T668" s="2" t="n">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="U668" s="2" t="n">
         <v>100</v>
@@ -55923,11 +55923,11 @@
       </c>
       <c r="S670" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T670" s="2" t="n">
-        <v>197</v>
+        <v>70</v>
       </c>
       <c r="U670" s="2" t="n">
         <v>50</v>
@@ -56085,11 +56085,11 @@
       </c>
       <c r="S672" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T672" s="2" t="n">
-        <v>192</v>
+        <v>70</v>
       </c>
       <c r="U672" s="2" t="n">
         <v>50</v>
@@ -56316,11 +56316,11 @@
       </c>
       <c r="S675" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T675" s="3" t="n">
-        <v>166</v>
+        <v>58</v>
       </c>
       <c r="U675" s="3" t="n">
         <v>50</v>
@@ -56478,11 +56478,11 @@
       </c>
       <c r="S677" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T677" s="3" t="n">
-        <v>175</v>
+        <v>67</v>
       </c>
       <c r="U677" s="3" t="n">
         <v>125</v>
@@ -56567,11 +56567,11 @@
       </c>
       <c r="S678" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T678" s="2" t="n">
-        <v>175</v>
+        <v>67</v>
       </c>
       <c r="U678" s="2" t="n">
         <v>100</v>
@@ -56729,11 +56729,11 @@
       </c>
       <c r="S680" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T680" s="2" t="n">
-        <v>176</v>
+        <v>63</v>
       </c>
       <c r="U680" s="2" t="n">
         <v>50</v>
@@ -56891,11 +56891,11 @@
       </c>
       <c r="S682" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T682" s="2" t="n">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="U682" s="2" t="n">
         <v>50</v>
@@ -57053,11 +57053,11 @@
       </c>
       <c r="S684" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T684" s="2" t="n">
-        <v>174</v>
+        <v>62</v>
       </c>
       <c r="U684" s="2" t="n">
         <v>50</v>
@@ -57215,11 +57215,11 @@
       </c>
       <c r="S686" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T686" s="2" t="n">
-        <v>185</v>
+        <v>65</v>
       </c>
       <c r="U686" s="2" t="n">
         <v>50</v>
@@ -57377,11 +57377,11 @@
       </c>
       <c r="S688" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T688" s="2" t="n">
-        <v>174</v>
+        <v>62</v>
       </c>
       <c r="U688" s="2" t="n">
         <v>50</v>
@@ -57539,11 +57539,11 @@
       </c>
       <c r="S690" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T690" s="2" t="n">
-        <v>184</v>
+        <v>67</v>
       </c>
       <c r="U690" s="2" t="n">
         <v>50</v>
@@ -57701,11 +57701,11 @@
       </c>
       <c r="S692" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T692" s="2" t="n">
-        <v>177</v>
+        <v>65</v>
       </c>
       <c r="U692" s="2" t="n">
         <v>50</v>
@@ -57867,11 +57867,11 @@
       </c>
       <c r="S694" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T694" s="2" t="n">
-        <v>201</v>
+        <v>71</v>
       </c>
       <c r="U694" s="2" t="n">
         <v>50</v>
@@ -58029,11 +58029,11 @@
       </c>
       <c r="S696" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T696" s="2" t="n">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="U696" s="2" t="n">
         <v>50</v>
@@ -58483,11 +58483,11 @@
       </c>
       <c r="S702" s="2" t="inlineStr">
         <is>
-          <t>pve</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T702" s="2" t="n">
-        <v>223</v>
+        <v>80</v>
       </c>
       <c r="U702" s="2" t="n">
         <v>125</v>
@@ -58572,11 +58572,11 @@
       </c>
       <c r="S703" s="3" t="inlineStr">
         <is>
-          <t>pve</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T703" s="3" t="n">
-        <v>223</v>
+        <v>80</v>
       </c>
       <c r="U703" s="3" t="n">
         <v>100</v>
@@ -58815,11 +58815,11 @@
       </c>
       <c r="S706" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T706" s="2" t="n">
-        <v>179</v>
+        <v>65</v>
       </c>
       <c r="U706" s="2" t="n">
         <v>200</v>
@@ -58977,11 +58977,11 @@
       </c>
       <c r="S708" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T708" s="2" t="n">
-        <v>175</v>
+        <v>62</v>
       </c>
       <c r="U708" s="2" t="n">
         <v>200</v>
@@ -59143,7 +59143,7 @@
         </is>
       </c>
       <c r="T710" s="2" t="n">
-        <v>214</v>
+        <v>78</v>
       </c>
       <c r="U710" s="2" t="n">
         <v>50</v>
@@ -59301,11 +59301,11 @@
       </c>
       <c r="S712" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T712" s="2" t="n">
-        <v>187</v>
+        <v>67</v>
       </c>
       <c r="U712" s="2" t="n">
         <v>400</v>
@@ -59905,11 +59905,11 @@
       </c>
       <c r="S720" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T720" s="2" t="n">
-        <v>187</v>
+        <v>67</v>
       </c>
       <c r="U720" s="2" t="n">
         <v>125</v>
@@ -59994,11 +59994,11 @@
       </c>
       <c r="S721" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T721" s="3" t="n">
-        <v>187</v>
+        <v>67</v>
       </c>
       <c r="U721" s="3" t="n">
         <v>100</v>
@@ -60156,11 +60156,11 @@
       </c>
       <c r="S723" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T723" s="3" t="n">
-        <v>198</v>
+        <v>71</v>
       </c>
       <c r="U723" s="3" t="n">
         <v>125</v>
@@ -60245,11 +60245,11 @@
       </c>
       <c r="S724" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T724" s="2" t="n">
-        <v>198</v>
+        <v>71</v>
       </c>
       <c r="U724" s="2" t="n">
         <v>100</v>
@@ -60407,11 +60407,11 @@
       </c>
       <c r="S726" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T726" s="2" t="n">
-        <v>204</v>
+        <v>73</v>
       </c>
       <c r="U726" s="2" t="n">
         <v>125</v>
@@ -60496,11 +60496,11 @@
       </c>
       <c r="S727" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T727" s="3" t="n">
-        <v>204</v>
+        <v>73</v>
       </c>
       <c r="U727" s="3" t="n">
         <v>100</v>
@@ -60658,11 +60658,11 @@
       </c>
       <c r="S729" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T729" s="3" t="n">
-        <v>182</v>
+        <v>67</v>
       </c>
       <c r="U729" s="3" t="n">
         <v>125</v>
@@ -60747,11 +60747,11 @@
       </c>
       <c r="S730" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T730" s="2" t="n">
-        <v>182</v>
+        <v>67</v>
       </c>
       <c r="U730" s="2" t="n">
         <v>100</v>
@@ -60905,11 +60905,11 @@
       </c>
       <c r="S732" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T732" s="2" t="n">
-        <v>168</v>
+        <v>61</v>
       </c>
       <c r="U732" s="2" t="n">
         <v>50</v>
@@ -61063,11 +61063,11 @@
       </c>
       <c r="S734" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T734" s="2" t="n">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="U734" s="2" t="n">
         <v>125</v>
@@ -61152,11 +61152,11 @@
       </c>
       <c r="S735" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T735" s="3" t="n">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="U735" s="3" t="n">
         <v>100</v>
@@ -61314,11 +61314,11 @@
       </c>
       <c r="S737" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T737" s="3" t="n">
-        <v>192</v>
+        <v>71</v>
       </c>
       <c r="U737" s="3" t="n">
         <v>50</v>
@@ -61557,11 +61557,11 @@
       </c>
       <c r="S740" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T740" s="2" t="n">
-        <v>165</v>
+        <v>59</v>
       </c>
       <c r="U740" s="2" t="n">
         <v>50</v>
@@ -61719,11 +61719,11 @@
       </c>
       <c r="S742" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T742" s="2" t="n">
-        <v>181</v>
+        <v>68</v>
       </c>
       <c r="U742" s="2" t="n">
         <v>50</v>
@@ -61881,11 +61881,11 @@
       </c>
       <c r="S744" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T744" s="2" t="n">
-        <v>162</v>
+        <v>60</v>
       </c>
       <c r="U744" s="2" t="n">
         <v>50</v>
@@ -62043,11 +62043,11 @@
       </c>
       <c r="S746" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T746" s="2" t="n">
-        <v>201</v>
+        <v>71</v>
       </c>
       <c r="U746" s="2" t="n">
         <v>50</v>
@@ -62205,11 +62205,11 @@
       </c>
       <c r="S748" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T748" s="2" t="n">
-        <v>164</v>
+        <v>58</v>
       </c>
       <c r="U748" s="2" t="n">
         <v>50</v>
@@ -62367,11 +62367,11 @@
       </c>
       <c r="S750" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T750" s="2" t="n">
-        <v>172</v>
+        <v>62</v>
       </c>
       <c r="U750" s="2" t="n">
         <v>50</v>
@@ -62529,11 +62529,11 @@
       </c>
       <c r="S752" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T752" s="2" t="n">
-        <v>156</v>
+        <v>54</v>
       </c>
       <c r="U752" s="2" t="n">
         <v>50</v>
@@ -62691,11 +62691,11 @@
       </c>
       <c r="S754" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T754" s="2" t="n">
-        <v>174</v>
+        <v>65</v>
       </c>
       <c r="U754" s="2" t="n">
         <v>50</v>
@@ -62853,11 +62853,11 @@
       </c>
       <c r="S756" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T756" s="2" t="n">
-        <v>204</v>
+        <v>74</v>
       </c>
       <c r="U756" s="2" t="n">
         <v>400</v>
@@ -63015,11 +63015,11 @@
       </c>
       <c r="S758" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T758" s="2" t="n">
-        <v>193</v>
+        <v>70</v>
       </c>
       <c r="U758" s="2" t="n">
         <v>125</v>
@@ -63104,11 +63104,11 @@
       </c>
       <c r="S759" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T759" s="3" t="n">
-        <v>193</v>
+        <v>70</v>
       </c>
       <c r="U759" s="3" t="n">
         <v>100</v>
@@ -63485,11 +63485,11 @@
       </c>
       <c r="S764" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T764" s="2" t="n">
-        <v>204</v>
+        <v>72</v>
       </c>
       <c r="U764" s="2" t="n">
         <v>400</v>
@@ -63647,11 +63647,11 @@
       </c>
       <c r="S766" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T766" s="2" t="n">
-        <v>178</v>
+        <v>63</v>
       </c>
       <c r="U766" s="2" t="n">
         <v>50</v>
@@ -64243,11 +64243,11 @@
       </c>
       <c r="S774" s="2" t="inlineStr">
         <is>
-          <t>pvp_gl</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T774" s="2" t="n">
-        <v>212</v>
+        <v>74</v>
       </c>
       <c r="U774" s="2" t="n">
         <v>125</v>
@@ -64332,11 +64332,11 @@
       </c>
       <c r="S775" s="3" t="inlineStr">
         <is>
-          <t>pvp_gl</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T775" s="3" t="n">
-        <v>212</v>
+        <v>74</v>
       </c>
       <c r="U775" s="3" t="n">
         <v>100</v>
@@ -64786,11 +64786,11 @@
       </c>
       <c r="S781" s="3" t="inlineStr">
         <is>
-          <t>pve</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T781" s="3" t="n">
-        <v>244</v>
+        <v>85</v>
       </c>
       <c r="U781" s="3" t="n">
         <v>125</v>
@@ -64875,11 +64875,11 @@
       </c>
       <c r="S782" s="2" t="inlineStr">
         <is>
-          <t>pve</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T782" s="2" t="n">
-        <v>244</v>
+        <v>85</v>
       </c>
       <c r="U782" s="2" t="n">
         <v>100</v>
@@ -65767,11 +65767,11 @@
       </c>
       <c r="S794" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T794" s="2" t="n">
-        <v>197</v>
+        <v>73</v>
       </c>
       <c r="U794" s="2" t="n">
         <v>200</v>
@@ -66075,11 +66075,11 @@
       </c>
       <c r="S798" s="2" t="inlineStr">
         <is>
-          <t>pve</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T798" s="2" t="n">
-        <v>229</v>
+        <v>81</v>
       </c>
       <c r="U798" s="2" t="n">
         <v>400</v>
@@ -66241,7 +66241,7 @@
         </is>
       </c>
       <c r="T800" s="2" t="n">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="U800" s="2" t="n">
         <v>125</v>
@@ -66330,7 +66330,7 @@
         </is>
       </c>
       <c r="T801" s="3" t="n">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="U801" s="3" t="n">
         <v>100</v>
@@ -66488,11 +66488,11 @@
       </c>
       <c r="S803" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T803" s="3" t="n">
-        <v>194</v>
+        <v>71</v>
       </c>
       <c r="U803" s="3" t="n">
         <v>125</v>
@@ -66577,11 +66577,11 @@
       </c>
       <c r="S804" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T804" s="2" t="n">
-        <v>194</v>
+        <v>71</v>
       </c>
       <c r="U804" s="2" t="n">
         <v>100</v>
@@ -66739,11 +66739,11 @@
       </c>
       <c r="S806" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T806" s="2" t="n">
-        <v>188</v>
+        <v>71</v>
       </c>
       <c r="U806" s="2" t="n">
         <v>125</v>
@@ -66828,11 +66828,11 @@
       </c>
       <c r="S807" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T807" s="3" t="n">
-        <v>188</v>
+        <v>71</v>
       </c>
       <c r="U807" s="3" t="n">
         <v>100</v>
@@ -66986,11 +66986,11 @@
       </c>
       <c r="S809" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T809" s="3" t="n">
-        <v>183</v>
+        <v>64</v>
       </c>
       <c r="U809" s="3" t="n">
         <v>50</v>
@@ -67144,11 +67144,11 @@
       </c>
       <c r="S811" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T811" s="3" t="n">
-        <v>184</v>
+        <v>64</v>
       </c>
       <c r="U811" s="3" t="n">
         <v>125</v>
@@ -67233,11 +67233,11 @@
       </c>
       <c r="S812" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T812" s="2" t="n">
-        <v>184</v>
+        <v>64</v>
       </c>
       <c r="U812" s="2" t="n">
         <v>100</v>
@@ -67395,11 +67395,11 @@
       </c>
       <c r="S814" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T814" s="2" t="n">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="U814" s="2" t="n">
         <v>50</v>
@@ -67557,11 +67557,11 @@
       </c>
       <c r="S816" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T816" s="2" t="n">
-        <v>164</v>
+        <v>56</v>
       </c>
       <c r="U816" s="2" t="n">
         <v>50</v>
@@ -67715,11 +67715,11 @@
       </c>
       <c r="S818" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T818" s="2" t="n">
-        <v>170</v>
+        <v>59</v>
       </c>
       <c r="U818" s="2" t="n">
         <v>50</v>
@@ -67873,11 +67873,11 @@
       </c>
       <c r="S820" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T820" s="2" t="n">
-        <v>165</v>
+        <v>59</v>
       </c>
       <c r="U820" s="2" t="n">
         <v>50</v>
@@ -68035,11 +68035,11 @@
       </c>
       <c r="S822" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T822" s="2" t="n">
-        <v>186</v>
+        <v>67</v>
       </c>
       <c r="U822" s="2" t="n">
         <v>125</v>
@@ -68124,11 +68124,11 @@
       </c>
       <c r="S823" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pvp_gl</t>
         </is>
       </c>
       <c r="T823" s="3" t="n">
-        <v>186</v>
+        <v>67</v>
       </c>
       <c r="U823" s="3" t="n">
         <v>100</v>
@@ -68286,11 +68286,11 @@
       </c>
       <c r="S825" s="3" t="inlineStr">
         <is>
-          <t>pvp_gl</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T825" s="3" t="n">
-        <v>210</v>
+        <v>74</v>
       </c>
       <c r="U825" s="3" t="n">
         <v>600</v>
@@ -68598,11 +68598,11 @@
       </c>
       <c r="S829" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T829" s="3" t="n">
-        <v>197</v>
+        <v>71</v>
       </c>
       <c r="U829" s="3" t="n">
         <v>50</v>
@@ -68760,11 +68760,11 @@
       </c>
       <c r="S831" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T831" s="3" t="n">
-        <v>182</v>
+        <v>66</v>
       </c>
       <c r="U831" s="3" t="n">
         <v>50</v>
@@ -68995,11 +68995,11 @@
       </c>
       <c r="S834" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T834" s="2" t="n">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="U834" s="2" t="n">
         <v>125</v>
@@ -69084,11 +69084,11 @@
       </c>
       <c r="S835" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T835" s="3" t="n">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="U835" s="3" t="n">
         <v>100</v>
@@ -69246,11 +69246,11 @@
       </c>
       <c r="S837" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T837" s="3" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="U837" s="3" t="n">
         <v>125</v>
@@ -69335,11 +69335,11 @@
       </c>
       <c r="S838" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T838" s="2" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="U838" s="2" t="n">
         <v>100</v>
@@ -70016,11 +70016,11 @@
       </c>
       <c r="S847" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T847" s="3" t="n">
-        <v>180</v>
+        <v>67</v>
       </c>
       <c r="U847" s="3" t="n">
         <v>400</v>
@@ -70474,7 +70474,7 @@
         </is>
       </c>
       <c r="T853" s="3" t="n">
-        <v>213</v>
+        <v>78</v>
       </c>
       <c r="U853" s="3" t="n">
         <v>125</v>
@@ -70563,7 +70563,7 @@
         </is>
       </c>
       <c r="T854" s="2" t="n">
-        <v>213</v>
+        <v>78</v>
       </c>
       <c r="U854" s="2" t="n">
         <v>100</v>
@@ -70944,7 +70944,7 @@
         </is>
       </c>
       <c r="T859" s="3" t="n">
-        <v>219</v>
+        <v>78</v>
       </c>
       <c r="U859" s="3" t="n">
         <v>200</v>
@@ -71759,11 +71759,11 @@
       </c>
       <c r="S870" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T870" s="2" t="n">
-        <v>186</v>
+        <v>69</v>
       </c>
       <c r="U870" s="2" t="n">
         <v>125</v>
@@ -71848,11 +71848,11 @@
       </c>
       <c r="S871" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T871" s="3" t="n">
-        <v>186</v>
+        <v>69</v>
       </c>
       <c r="U871" s="3" t="n">
         <v>100</v>
@@ -72010,11 +72010,11 @@
       </c>
       <c r="S873" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T873" s="3" t="n">
-        <v>202</v>
+        <v>71</v>
       </c>
       <c r="U873" s="3" t="n">
         <v>125</v>
@@ -72099,11 +72099,11 @@
       </c>
       <c r="S874" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T874" s="2" t="n">
-        <v>202</v>
+        <v>71</v>
       </c>
       <c r="U874" s="2" t="n">
         <v>100</v>
@@ -72261,11 +72261,11 @@
       </c>
       <c r="S876" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T876" s="2" t="n">
-        <v>194</v>
+        <v>71</v>
       </c>
       <c r="U876" s="2" t="n">
         <v>125</v>
@@ -72350,11 +72350,11 @@
       </c>
       <c r="S877" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T877" s="3" t="n">
-        <v>194</v>
+        <v>71</v>
       </c>
       <c r="U877" s="3" t="n">
         <v>100</v>
@@ -72508,11 +72508,11 @@
       </c>
       <c r="S879" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T879" s="3" t="n">
-        <v>187</v>
+        <v>67</v>
       </c>
       <c r="U879" s="3" t="n">
         <v>50</v>
@@ -72666,11 +72666,11 @@
       </c>
       <c r="S881" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T881" s="3" t="n">
-        <v>151</v>
+        <v>51</v>
       </c>
       <c r="U881" s="3" t="n">
         <v>25</v>
@@ -72828,11 +72828,11 @@
       </c>
       <c r="S883" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T883" s="3" t="n">
-        <v>169</v>
+        <v>61</v>
       </c>
       <c r="U883" s="3" t="n">
         <v>50</v>
@@ -72990,11 +72990,11 @@
       </c>
       <c r="S885" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T885" s="3" t="n">
-        <v>178</v>
+        <v>66</v>
       </c>
       <c r="U885" s="3" t="n">
         <v>125</v>
@@ -73079,11 +73079,11 @@
       </c>
       <c r="S886" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T886" s="2" t="n">
-        <v>178</v>
+        <v>66</v>
       </c>
       <c r="U886" s="2" t="n">
         <v>100</v>
@@ -73237,11 +73237,11 @@
       </c>
       <c r="S888" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T888" s="2" t="n">
-        <v>162</v>
+        <v>56</v>
       </c>
       <c r="U888" s="2" t="n">
         <v>50</v>
@@ -73395,11 +73395,11 @@
       </c>
       <c r="S890" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T890" s="2" t="n">
-        <v>168</v>
+        <v>58</v>
       </c>
       <c r="U890" s="2" t="n">
         <v>50</v>
@@ -73557,11 +73557,11 @@
       </c>
       <c r="S892" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T892" s="2" t="n">
-        <v>194</v>
+        <v>70</v>
       </c>
       <c r="U892" s="2" t="n">
         <v>125</v>
@@ -73646,11 +73646,11 @@
       </c>
       <c r="S893" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T893" s="3" t="n">
-        <v>194</v>
+        <v>70</v>
       </c>
       <c r="U893" s="3" t="n">
         <v>100</v>
@@ -73812,7 +73812,7 @@
         </is>
       </c>
       <c r="T895" s="3" t="n">
-        <v>196</v>
+        <v>70</v>
       </c>
       <c r="U895" s="3" t="n">
         <v>125</v>
@@ -73901,7 +73901,7 @@
         </is>
       </c>
       <c r="T896" s="2" t="n">
-        <v>196</v>
+        <v>70</v>
       </c>
       <c r="U896" s="2" t="n">
         <v>100</v>
@@ -74059,11 +74059,11 @@
       </c>
       <c r="S898" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T898" s="2" t="n">
-        <v>203</v>
+        <v>73</v>
       </c>
       <c r="U898" s="2" t="n">
         <v>50</v>
@@ -74294,11 +74294,11 @@
       </c>
       <c r="S901" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T901" s="3" t="n">
-        <v>190</v>
+        <v>67</v>
       </c>
       <c r="U901" s="3" t="n">
         <v>50</v>
@@ -74456,11 +74456,11 @@
       </c>
       <c r="S903" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T903" s="3" t="n">
-        <v>173</v>
+        <v>64</v>
       </c>
       <c r="U903" s="3" t="n">
         <v>50</v>
@@ -74618,11 +74618,11 @@
       </c>
       <c r="S905" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T905" s="3" t="n">
-        <v>166</v>
+        <v>60</v>
       </c>
       <c r="U905" s="3" t="n">
         <v>50</v>
@@ -74780,11 +74780,11 @@
       </c>
       <c r="S907" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T907" s="3" t="n">
-        <v>180</v>
+        <v>63</v>
       </c>
       <c r="U907" s="3" t="n">
         <v>50</v>
@@ -75015,11 +75015,11 @@
       </c>
       <c r="S910" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T910" s="2" t="n">
-        <v>173</v>
+        <v>60</v>
       </c>
       <c r="U910" s="2" t="n">
         <v>125</v>
@@ -75104,11 +75104,11 @@
       </c>
       <c r="S911" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T911" s="3" t="n">
-        <v>173</v>
+        <v>60</v>
       </c>
       <c r="U911" s="3" t="n">
         <v>100</v>
@@ -75266,11 +75266,11 @@
       </c>
       <c r="S913" s="3" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T913" s="3" t="n">
-        <v>153</v>
+        <v>55</v>
       </c>
       <c r="U913" s="3" t="n">
         <v>50</v>
@@ -75501,11 +75501,11 @@
       </c>
       <c r="S916" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T916" s="2" t="n">
-        <v>192</v>
+        <v>70</v>
       </c>
       <c r="U916" s="2" t="n">
         <v>50</v>
@@ -75663,11 +75663,11 @@
       </c>
       <c r="S918" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T918" s="2" t="n">
-        <v>205</v>
+        <v>74</v>
       </c>
       <c r="U918" s="2" t="n">
         <v>50</v>
@@ -75825,11 +75825,11 @@
       </c>
       <c r="S920" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T920" s="2" t="n">
-        <v>179</v>
+        <v>64</v>
       </c>
       <c r="U920" s="2" t="n">
         <v>50</v>
@@ -75991,7 +75991,7 @@
         </is>
       </c>
       <c r="T922" s="2" t="n">
-        <v>216</v>
+        <v>76</v>
       </c>
       <c r="U922" s="2" t="n">
         <v>50</v>
@@ -76587,7 +76587,7 @@
         </is>
       </c>
       <c r="T930" s="2" t="n">
-        <v>217</v>
+        <v>78</v>
       </c>
       <c r="U930" s="2" t="n">
         <v>125</v>
@@ -76676,7 +76676,7 @@
         </is>
       </c>
       <c r="T931" s="3" t="n">
-        <v>217</v>
+        <v>78</v>
       </c>
       <c r="U931" s="3" t="n">
         <v>100</v>
@@ -76980,11 +76980,11 @@
       </c>
       <c r="S935" s="3" t="inlineStr">
         <is>
-          <t>pvp_gl</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T935" s="3" t="n">
-        <v>210</v>
+        <v>74</v>
       </c>
       <c r="U935" s="3" t="n">
         <v>400</v>
@@ -77069,11 +77069,11 @@
       </c>
       <c r="S936" s="2" t="inlineStr">
         <is>
-          <t>coleccionable</t>
+          <t>pve</t>
         </is>
       </c>
       <c r="T936" s="2" t="n">
-        <v>192</v>
+        <v>69</v>
       </c>
       <c r="U936" s="2" t="n">
         <v>50</v>
